--- a/排阵/对阵表_LLM.xlsx
+++ b/排阵/对阵表_LLM.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="对阵表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="球员统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,11 +38,6 @@
       <name val="微软雅黑"/>
       <b val="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -91,15 +85,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,33 +451,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>科技球队日常训练活动 - 对阵表（2026年03月23日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
+          <t>科技球队日常训练活动 - 对阵表（2026年04月13日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>场地数：2个 | 时长：2 小时 | 赛制：15 分/局，2 局 | 项目：男双、女双、混双 | 排阵方式：LLM 推理</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
+          <t>场地数：3个 | 时长：2 小时 | 赛制：15 分/局，2 局 | 项目：男双、女双、混双</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>轮次</t>
@@ -529,40 +514,44 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="4" t="n">
-        <v>1</v>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>第1轮</t>
+        </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>1号</t>
+          <t>1号场地</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/崔倩男</t>
+          <t>李祺祺/滕菲</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr"/>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>林锋/李祺祺</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>1</v>
+          <t>崔倩男/田茜</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>第1轮</t>
+        </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2号</t>
+          <t>2号场地</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -572,24 +561,26 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>严勇文/陈小洪</t>
+          <t>严勇文/卢志辉</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>王小波/刘继宇</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>2</v>
+          <t>苏大哲/刘继宇</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>第1轮</t>
+        </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1号</t>
+          <t>3号场地</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -599,24 +590,26 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>严勇文/江锐</t>
+          <t>林锋/罗琴荩</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/张欣欣</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>2</v>
+          <t>罗蒙/王小波</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>第2轮</t>
+        </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2号</t>
+          <t>1号场地</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -626,105 +619,113 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>王小波/崔倩男</t>
+          <t>罗蒙/李祺祺</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>林锋/高洁</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>3</v>
+          <t>罗琴荩/崔倩男</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>第2轮</t>
+        </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1号</t>
+          <t>2号场地</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/崔倩男</t>
+          <t>严勇文/陈顺星</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/李祺祺</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>3</v>
+          <t>黄冬青/陈小洪</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>第2轮</t>
+        </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2号</t>
+          <t>3号场地</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>严勇文/江锐</t>
+          <t>林锋/滕菲</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/陈小洪</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>4</v>
+          <t>王小波/田茜</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1号</t>
+          <t>1号场地</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>林锋/崔倩男</t>
+          <t>李祺祺/田茜</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/高洁</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>4</v>
+          <t>滕菲/崔倩男</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2号</t>
+          <t>2号场地</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -734,24 +735,26 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>严勇文/罗蒙</t>
+          <t>严勇文/刘继宇</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
       <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>王小波/张欣欣</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>5</v>
+          <t>陈顺星/陈小洪</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>1号</t>
+          <t>3号场地</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -761,24 +764,26 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>严勇文/陈小洪</t>
+          <t>黄冬青/卢志辉</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>江锐/刘继宇</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>5</v>
+          <t>罗蒙/林锋</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>第4轮</t>
+        </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2号</t>
+          <t>1号场地</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -788,105 +793,113 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/崔倩男</t>
+          <t>罗蒙/李祺祺</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>王小波/李祺祺</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>6</v>
+          <t>陈顺星/崔倩男</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>第4轮</t>
+        </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>1号</t>
+          <t>2号场地</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>男双</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>林锋/李祺祺</t>
+          <t>严勇文/苏大哲</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/高洁</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>6</v>
+          <t>刘继宇/卢志辉</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>第4轮</t>
+        </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2号</t>
+          <t>3号场地</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>男双</t>
+          <t>混双</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>江锐/张欣欣</t>
+          <t>王小波/滕菲</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/陈小洪</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>7</v>
+          <t>罗琴荩/田茜</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>第5轮</t>
+        </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>1号</t>
+          <t>1号场地</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>混双</t>
+          <t>女双</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/李祺祺</t>
+          <t>李祺祺/崔倩男</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>王小波/高洁</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>7</v>
+          <t>滕菲/田茜</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>第5轮</t>
+        </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2号</t>
+          <t>2号场地</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -896,24 +909,26 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/陈顺星</t>
+          <t>苏大哲/陈小洪</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>江锐/张欣欣</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>8</v>
+          <t>严勇文/黄冬青</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>第5轮</t>
+        </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>1号</t>
+          <t>3号场地</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -923,24 +938,26 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>江锐/林锋</t>
+          <t>罗蒙/林锋</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
       <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>陈小洪/张欣欣</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>8</v>
+          <t>王小波/罗琴荩</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>第6轮</t>
+        </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2号</t>
+          <t>1号场地</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -950,14 +967,246 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>刘继宇/陈顺星</t>
+          <t>苏大哲/罗琴荩</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>罗蒙/王小波</t>
+          <t>刘继宇/卢志辉</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>第6轮</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2号场地</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>陈顺星/陈小洪</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>王小波/黄冬青</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>第6轮</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>3号场地</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>混双</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>林锋/滕菲</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>罗蒙/田茜</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>第7轮</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>1号场地</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>苏大哲/刘继宇</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>卢志辉/黄冬青</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>第7轮</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2号场地</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>混双</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>王小波/田茜</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>罗蒙/滕菲</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>第7轮</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>3号场地</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>混双</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>陈顺星/李祺祺</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>林锋/陈小洪</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>第8轮</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>1号场地</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>男双</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>苏大哲/陈小洪</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>刘继宇/陈顺星</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>第8轮</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2号场地</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>混双</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>罗蒙/滕菲</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>罗琴荩/田茜</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>第8轮</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>3号场地</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>混双</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>卢志辉/王小波</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>林锋/李祺祺</t>
         </is>
       </c>
     </row>
@@ -966,293 +1215,6 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>球员参赛场次统计</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>姓名</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>总场次</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>男双</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>女双</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>混双</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>严勇文</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>刘继宇</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>张欣欣</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>林锋</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>江锐</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>王小波</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>罗蒙</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>陈小洪</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>陈顺星</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>崔倩男</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>李祺祺</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>高洁</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/排阵/对阵表_LLM.xlsx
+++ b/排阵/对阵表_LLM.xlsx
@@ -996,14 +996,14 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>陈顺星/陈小洪</t>
+          <t>陈顺星/黄冬青</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>王小波/黄冬青</t>
+          <t>王小波/陈小洪</t>
         </is>
       </c>
     </row>
